--- a/docs/export-templates/AI问书_全域机构账户导入模板.xlsx
+++ b/docs/export-templates/AI问书_全域机构账户导入模板.xlsx
@@ -16,9 +16,17 @@
     <t>机构账户批量导入模板</t>
   </si>
   <si>
-    <t xml:space="preserve">填写说明：1）单次最多 500 条，超出请拆分文件分批导入；2）按「账户名」匹配：已存在则更新，不存在则新建；3）新建时账户名 / 姓名 / 机构 / 角色必填；密码留空由系统生成；4）更新时留空的单元格不修改；填写密码即重置为该密码
-账户名：3–32 位，字母、数字或 _ - . @，不含空格与中文；密码：8–16 位，同时含字母和数字，不含空格；机构：XX 出版集团 / YY 教育 / ZZ 少儿；角色：管理员 / 运营 / 只读；联系电话：11 位手机号，可留空。
-赭色表头为新建必填列。请从第 4 行开始填写，不要修改表头。</t>
+    <t xml:space="preserve">填写说明：
+1. 单次最多 500 条，超出请拆分文件分批导入
+2. 按「账户名」匹配：已存在则更新，不存在则新建
+3. 新建时账户名 / 姓名 / 机构 / 角色必填；密码留空由系统生成
+4. 更新时留空的单元格不修改；填写密码即重置为该密码
+5. 上传后先预览、确认后导入；有误的行跳过、其余照常导入，导入后弹窗告知成功数与失败明细（行号 + 原因）
+6. 账户名：3–32 位，字母、数字或 _ - . @，不含空格与中文
+7. 密码：8–16 位，同时含字母和数字，不含空格
+8. 机构：XX 出版集团 / YY 教育 / ZZ 少儿；角色：管理员 / 运营 / 只读（均可下拉选择）
+9. 联系电话：11 位手机号，可留空
+10. 赭色表头为新建必填列；请从第 4 行开始填写，不要修改表头</t>
   </si>
   <si>
     <t>账户名</t>
@@ -478,7 +486,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" ht="78" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" ht="173" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
